--- a/nr-update-change-notes/ig/ValueSet-fr-core-vs-bp-method.xlsx
+++ b/nr-update-change-notes/ig/ValueSet-fr-core-vs-bp-method.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:25:22+00:00</t>
+    <t>2025-07-07T15:26:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-change-notes/ig/ValueSet-fr-core-vs-bp-method.xlsx
+++ b/nr-update-change-notes/ig/ValueSet-fr-core-vs-bp-method.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:26:46+00:00</t>
+    <t>2025-10-08T07:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-change-notes/ig/ValueSet-fr-core-vs-bp-method.xlsx
+++ b/nr-update-change-notes/ig/ValueSet-fr-core-vs-bp-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:41:56+00:00</t>
+    <t>2025-10-08T15:42:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
